--- a/04_DESIGN_TABLES/DesignTable_2650.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2650.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,7 +582,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -592,12 +592,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p062-t02: agrees on M1@DRIVE, M2@DRIVE, M3@DRIVE, M4@DRIVE, Y@HEX, D1@BORE, D2@BORE, D3@BORE, D4@BORE</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2650-04-04-04-04-FG</t>
         </is>
       </c>
     </row>
